--- a/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ6を新設し2件追加（TC-048〜049）。048＝集計対象を紙版のみに限定したこと（顧客要件2026-08 / #56408・API設計書 v1.2）。本帳票は販売店へ配達部数の増減を伝えるもので電子版・併読には配達の概念が無い。従来の「電子版は承認済のみ集計」条件は紙版限定に包含されるため廃止された。049＝販売店候補から電子版ダミー販売店(9999999999)を除外したこと（#56597・`dummy=exclude`）。廃店(`haiten_flg=true`)も候補に出ないことを併せて確認する</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ56"/>
+  <dimension ref="A1:BQ64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11210,20 +11268,20 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="128" customHeight="1">
+    <row r="40" ht="160" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-025</t>
+          <t>ACSMS-TC-028-041</t>
         </is>
       </c>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>増減報告フラグ＋適用日一致での抽出</t>
+          <t>同日複数履歴の累計（1→3→5 を 1→5）</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -11233,7 +11291,7 @@
       <c r="J40" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・適用日と一致する履歴、および増減報告対象外（zougen_hokoku_flg=false）の履歴が存在する</t>
+・同一購読者が同じ適用日に部数を 1→3→5 と複数回変更した履歴が存在する（同日2レコード以上）</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -11258,7 +11316,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日を入力して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>増部テーブルの該当購読者を確認する</t>
           </r>
         </is>
       </c>
@@ -11284,15 +11359,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・`joho_henko_tekiyo_date = 適用日` かつ `zougen_hokoku_flg = true` のレコードのみが抽出されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・適用日が一致しない、または増減報告対象外のレコードが表示されないこと</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・該当購読者が **2行ではなく1行** で表示されること（同日累計）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・部数が **「1 → 5」**（日初の前回部数 → 日末の現部数）で表示されること</t>
           </r>
         </is>
       </c>
@@ -11346,20 +11438,20 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="64" customHeight="1">
+    <row r="41" ht="128" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-026</t>
+          <t>ACSMS-TC-028-042</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>廃店の除外</t>
+          <t>解約（…→0）が減部に反映</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -11369,7 +11461,7 @@
       <c r="J41" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・廃店（haiten_flg=true）に紐づく履歴が存在する</t>
+・当該適用日に解約（購読部数 2→0）した購読者が存在する</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -11394,7 +11486,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日を入力して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>減部テーブルの内容を確認する</t>
           </r>
         </is>
       </c>
@@ -11420,7 +11529,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>廃店（haiten_flg=true）に紐づくレコードが抽出されないこと</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・解約購読者が減部テーブルに表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・部数が **「2 → 0」** で表示されること</t>
           </r>
         </is>
       </c>
@@ -11474,20 +11608,20 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="64" customHeight="1">
+    <row r="42" ht="160" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-027</t>
+          <t>ACSMS-TC-028-043</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>販売店フィルタ</t>
+          <t>販売店変更（旧店に減 / 新店に増）</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -11497,7 +11631,7 @@
       <c r="J42" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・複数の販売店に対象データが存在する</t>
+・当該適用日に販売店を A→B に変更した購読者が存在する（部数は不変 1→1）</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -11522,7 +11656,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日と特定の販売店を選択して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>旧販売店A・新販売店B それぞれの帳票を確認する</t>
           </r>
         </is>
       </c>
@@ -11548,7 +11699,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>選択した販売店に紐づくレコードのみが抽出されること</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・旧販売店A の **減部** に当該購読者が表示されること（部数「1 → 0」）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新販売店B の **増部** に当該購読者が表示されること（部数「0 → 1」）</t>
           </r>
         </is>
       </c>
@@ -11594,7 +11770,11 @@
       <c r="BH42" s="45" t="inlineStr"/>
       <c r="BI42" s="10" t="n"/>
       <c r="BJ42" s="11" t="n"/>
-      <c r="BK42" s="46" t="inlineStr"/>
+      <c r="BK42" s="46" t="inlineStr">
+        <is>
+          <t>旧販売店の管理支店は履歴に保持されないため、暫定的に当日最終レコードの管理支店を用いる。</t>
+        </is>
+      </c>
       <c r="BL42" s="10" t="n"/>
       <c r="BM42" s="10" t="n"/>
       <c r="BN42" s="10" t="n"/>
@@ -11602,20 +11782,20 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="64" customHeight="1">
+    <row r="43" ht="144" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-028</t>
+          <t>ACSMS-TC-028-044</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="46" t="inlineStr">
         <is>
-          <t>管理支店フィルタ</t>
+          <t>新規購読者は住所変更に出さない</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -11625,7 +11805,7 @@
       <c r="J43" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・複数の管理支店に対象データが存在する</t>
+・当該適用日に新規購読開始した購読者（初回履歴・前回住所が空）が存在する</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -11650,7 +11830,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日と特定の管理支店を選択して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>増部テーブルと住所変更テーブルを確認する</t>
           </r>
         </is>
       </c>
@@ -11676,7 +11873,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>選択した管理支店に紐づくレコードのみが抽出されること</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・新規購読者が **増部**（「0 → 1」）に表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新規購読者が **住所変更テーブルには表示されない** こと（前回住所が空のため）</t>
           </r>
         </is>
       </c>
@@ -11730,20 +11952,20 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="128" customHeight="1">
+    <row r="44" ht="400" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-029</t>
+          <t>ACSMS-TC-028-047</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="46" t="inlineStr">
         <is>
-          <t>対象0件（プレビュー）</t>
+          <t>ページ送り（SQL OFFSET/LIMIT・購読者単位・別API）</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -11753,7 +11975,7 @@
       <c r="J44" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・指定した条件に対象データが存在しない</t>
+・当該適用日に 16 名以上の増減対象購読者が存在する</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
@@ -11778,7 +12000,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>対象が存在しない適用日・条件で「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>プレビュー下部のページャで 2 ページ目に移動する</t>
           </r>
         </is>
       </c>
@@ -11804,15 +12043,72 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`reports:[]`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-028-002、トーストではない）</t>
+            <t xml:space="preserve">・1ページ目に **15 購読者**まで表示されること（≒15レコード。大半1レコード/購読者。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店変更=2 / 部数+住所変更=2 になり得るため厳密に15行ではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ページャ（全N件＝対象購読者数・1/M ページ）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・帳票ヘッダの「ページ数」が `1/M` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・BEは `COUNT(DISTINCT dokusya_id)` ＋ `dokusya_id` の OFFSET/LIMIT で1ページ分の
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者の明細だけをロードすること（全件ロードではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・2 ページ目を別APIで再取得し、残りの購読者が表示されること（ブラウザは1ページ分のみ描画）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「ページ数」が `2/M` に更新されること</t>
           </r>
         </is>
       </c>
@@ -11824,7 +12120,7 @@
       <c r="AD44" s="11" t="n"/>
       <c r="AE44" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF44" s="11" t="n"/>
@@ -11858,7 +12154,11 @@
       <c r="BH44" s="45" t="inlineStr"/>
       <c r="BI44" s="10" t="n"/>
       <c r="BJ44" s="11" t="n"/>
-      <c r="BK44" s="46" t="inlineStr"/>
+      <c r="BK44" s="46" t="inlineStr">
+        <is>
+          <t>電子帳票（PDF）出力はページングせず全件を1つのPDFに出力する。</t>
+        </is>
+      </c>
       <c r="BL44" s="10" t="n"/>
       <c r="BM44" s="10" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -11866,20 +12166,20 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="288" customHeight="1">
+    <row r="45" ht="128" customHeight="1">
       <c r="A45" s="44" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-030</t>
+          <t>ACSMS-TC-028-025</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>電子帳票（PDF）出力 正常系・内容</t>
+          <t>増減報告フラグ＋適用日一致での抽出</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -11889,7 +12189,7 @@
       <c r="J45" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・適用日に対象データが存在する</t>
+・適用日と一致する履歴、および増減報告対象外（zougen_hokoku_flg=false）の履歴が存在する</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
@@ -11914,24 +12214,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日・販売店・管理支店を選択して「電子帳票作成」を実行する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>ダウンロードしたPDFを開き、内容を確認する</t>
+            <t>適用日を入力して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -11957,48 +12240,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PDFファイルがダウンロードされること（ファイル名 `増減連絡票_販売店_{YYYY年MM月DD日}.pdf`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・販売店＋管理支店の組み合わせごとに1枚で出力され、販売店コード昇順で改ページされること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・ヘッダに販売店名・管理支店名・管理支店のTEL/FAX・ページ数が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・増部／減部／住所変更の3テーブルが表示されること</t>
+            <t xml:space="preserve">・`joho_henko_tekiyo_date = 適用日` かつ `zougen_hokoku_flg = true` のレコードのみが抽出されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・適用日が一致しない、または増減報告対象外のレコードが表示されないこと</t>
           </r>
         </is>
       </c>
@@ -12052,20 +12302,20 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="400" customHeight="1">
+    <row r="46" ht="64" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-031</t>
+          <t>ACSMS-TC-028-026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>ダウンロード履歴・操作ログ記録</t>
+          <t>廃店の除外</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -12074,7 +12324,8 @@
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・廃店（haiten_flg=true）に紐づく履歴が存在する</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -12099,120 +12350,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「電子帳票作成」を実行する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、ダウンロード履歴と操作ログを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_file_download
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY download_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減連絡票（販売店）出力画面 (ACSMS-SCR-028)'
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>適用日を入力して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12238,32 +12376,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">PDFファイルがダウンロードされること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・t_file_download に1件登録されること（download_type=3、file_name にPDFファイル名、record_count に対象件数、target_month に適用日の年月）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・t_log に監査ログが1件記録されること（log_type=1、operation=`EXPORT_PDF`、result_status=1、target_table=`t_file_download`）</t>
+            <t>廃店（haiten_flg=true）に紐づくレコードが抽出されないこと</t>
           </r>
         </is>
       </c>
@@ -12317,20 +12430,20 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="256" customHeight="1">
+    <row r="47" ht="64" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-032</t>
+          <t>ACSMS-TC-028-027</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>トランザクション ロールバック</t>
+          <t>販売店フィルタ</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -12340,7 +12453,7 @@
       <c r="J47" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・ダウンロード履歴登録時にDBエラーを発生させる準備ができている</t>
+・複数の販売店に対象データが存在する</t>
         </is>
       </c>
       <c r="K47" s="10" t="n"/>
@@ -12365,24 +12478,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「電子帳票作成」を実行する（DB登録の途中でエラーを注入する）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DBで t_file_download・t_log の状態を確認</t>
+            <t>適用日と特定の販売店を選択して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12408,32 +12504,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・t_file_download・t_log（log_type=1）のいずれも登録されないこと（ロールバックされること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・t_log にエラーログが1件記録されること（log_type=3、result_status=2）</t>
+            <t>選択した販売店に紐づくレコードのみが抽出されること</t>
           </r>
         </is>
       </c>
@@ -12445,7 +12516,7 @@
       <c r="AD47" s="11" t="n"/>
       <c r="AE47" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF47" s="11" t="n"/>
@@ -12487,20 +12558,20 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="224" customHeight="1">
+    <row r="48" ht="64" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-033</t>
+          <t>ACSMS-TC-028-028</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>対象0件（電子帳票作成）</t>
+          <t>管理支店フィルタ</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -12510,7 +12581,7 @@
       <c r="J48" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・指定した条件に対象データが存在しない</t>
+・複数の管理支店に対象データが存在する</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -12535,24 +12606,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象が存在しない適用日・条件で「電子帳票作成」を実行する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DBで t_file_download の登録件数を確認する</t>
+            <t>適用日と特定の管理支店を選択して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12578,40 +12632,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`application/json` の `{ data: { reports: [] } }`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PDFファイルがダウンロードされないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-028-002）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>t_file_download にレコードが登録されないこと</t>
+            <t>選択した管理支店に紐づくレコードのみが抽出されること</t>
           </r>
         </is>
       </c>
@@ -12623,7 +12644,7 @@
       <c r="AD48" s="11" t="n"/>
       <c r="AE48" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF48" s="11" t="n"/>
@@ -12657,12 +12678,7 @@
       <c r="BH48" s="45" t="inlineStr"/>
       <c r="BI48" s="10" t="n"/>
       <c r="BJ48" s="11" t="n"/>
-      <c r="BK48" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK48" s="46" t="inlineStr"/>
       <c r="BL48" s="10" t="n"/>
       <c r="BM48" s="10" t="n"/>
       <c r="BN48" s="10" t="n"/>
@@ -12670,74 +12686,135 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="32" t="inlineStr">
-        <is>
-          <t>カテゴリ5: 共通エラーハンドリング（Common Error Handling）</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n"/>
+    <row r="49" ht="128" customHeight="1">
+      <c r="A49" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-029</t>
+        </is>
+      </c>
       <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>対象0件（プレビュー）</t>
+        </is>
+      </c>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・指定した条件に対象データが存在しない</t>
+        </is>
+      </c>
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>対象が存在しない適用日・条件で「レポートプレビュー」を実行する</t>
+          </r>
+        </is>
+      </c>
       <c r="R49" s="10" t="n"/>
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
+      <c r="W49" s="11" t="n"/>
+      <c r="X49" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`reports:[]`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-028-002、トーストではない）</t>
+          </r>
+        </is>
+      </c>
       <c r="Y49" s="10" t="n"/>
       <c r="Z49" s="10" t="n"/>
       <c r="AA49" s="10" t="n"/>
       <c r="AB49" s="10" t="n"/>
       <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF49" s="11" t="n"/>
+      <c r="AG49" s="45" t="inlineStr"/>
       <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
+      <c r="AI49" s="11" t="n"/>
+      <c r="AJ49" s="45" t="inlineStr"/>
       <c r="AK49" s="10" t="n"/>
-      <c r="AL49" s="10" t="n"/>
-      <c r="AM49" s="10" t="n"/>
+      <c r="AL49" s="11" t="n"/>
+      <c r="AM49" s="45" t="inlineStr"/>
       <c r="AN49" s="10" t="n"/>
-      <c r="AO49" s="10" t="n"/>
-      <c r="AP49" s="10" t="n"/>
+      <c r="AO49" s="11" t="n"/>
+      <c r="AP49" s="45" t="inlineStr"/>
       <c r="AQ49" s="10" t="n"/>
-      <c r="AR49" s="10" t="n"/>
-      <c r="AS49" s="10" t="n"/>
+      <c r="AR49" s="11" t="n"/>
+      <c r="AS49" s="45" t="inlineStr"/>
       <c r="AT49" s="10" t="n"/>
-      <c r="AU49" s="10" t="n"/>
-      <c r="AV49" s="10" t="n"/>
+      <c r="AU49" s="11" t="n"/>
+      <c r="AV49" s="45" t="inlineStr"/>
       <c r="AW49" s="10" t="n"/>
-      <c r="AX49" s="10" t="n"/>
-      <c r="AY49" s="10" t="n"/>
+      <c r="AX49" s="11" t="n"/>
+      <c r="AY49" s="45" t="inlineStr"/>
       <c r="AZ49" s="10" t="n"/>
-      <c r="BA49" s="10" t="n"/>
-      <c r="BB49" s="10" t="n"/>
+      <c r="BA49" s="11" t="n"/>
+      <c r="BB49" s="45" t="inlineStr"/>
       <c r="BC49" s="10" t="n"/>
-      <c r="BD49" s="10" t="n"/>
-      <c r="BE49" s="10" t="n"/>
+      <c r="BD49" s="11" t="n"/>
+      <c r="BE49" s="45" t="inlineStr"/>
       <c r="BF49" s="10" t="n"/>
-      <c r="BG49" s="10" t="n"/>
-      <c r="BH49" s="10" t="n"/>
+      <c r="BG49" s="11" t="n"/>
+      <c r="BH49" s="45" t="inlineStr"/>
       <c r="BI49" s="10" t="n"/>
-      <c r="BJ49" s="10" t="n"/>
-      <c r="BK49" s="10" t="n"/>
+      <c r="BJ49" s="11" t="n"/>
+      <c r="BK49" s="46" t="inlineStr"/>
       <c r="BL49" s="10" t="n"/>
       <c r="BM49" s="10" t="n"/>
       <c r="BN49" s="10" t="n"/>
@@ -12745,20 +12822,20 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="112" customHeight="1">
+    <row r="50" ht="288" customHeight="1">
       <c r="A50" s="44" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-034</t>
+          <t>ACSMS-TC-028-030</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>不正リクエストパラメータ（BAD_REQUEST）</t>
+          <t>電子帳票（PDF）出力 正常系・内容</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -12767,7 +12844,8 @@
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・適用日に対象データが存在する</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -12792,7 +12870,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsのNetworkタブでGET「/api/v1/report/zougen-hanbaiten/preview?tekiyo_date=2026-05-01&amp;hanbaiten_id=abc」（数値項目に文字列）を送信</t>
+            <t xml:space="preserve">適用日・販売店・管理支店を選択して「電子帳票作成」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>ダウンロードしたPDFを開き、内容を確認する</t>
           </r>
         </is>
       </c>
@@ -12818,7 +12913,48 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。` または `error_code: VALIDATION_ERROR`）</t>
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PDFファイルがダウンロードされること（ファイル名 `増減連絡票_販売店_{YYYY年MM月DD日}.pdf`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・販売店＋管理支店の組み合わせごとに1枚で出力され、販売店コード昇順で改ページされること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ヘッダに販売店名・管理支店名・管理支店のTEL/FAX・ページ数が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・増部／減部／住所変更の3テーブルが表示されること</t>
           </r>
         </is>
       </c>
@@ -12830,7 +12966,7 @@
       <c r="AD50" s="11" t="n"/>
       <c r="AE50" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF50" s="11" t="n"/>
@@ -12872,20 +13008,20 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="208" customHeight="1">
+    <row r="51" ht="400" customHeight="1">
       <c r="A51" s="44" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-035</t>
+          <t>ACSMS-TC-028-031</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>セッション切れ（UNAUTHORIZED）</t>
+          <t>ダウンロード履歴・操作ログ記録</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -12894,8 +13030,7 @@
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み
-・管理ツールでセッションを強制失効させる準備ができている</t>
+          <t>・CHUOKAI でログイン済み</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -12920,7 +13055,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">増減連絡票（販売店）出力画面を開いた状態でセッションを強制失効させる
+            <t xml:space="preserve">「電子帳票作成」を実行する
 </t>
           </r>
           <r>
@@ -12937,7 +13072,103 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「レポートプレビュー」ボタンをクリックする</t>
+            <t xml:space="preserve">DBで以下クエリを実行し、ダウンロード履歴と操作ログを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_file_download
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY download_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減連絡票（販売店）出力画面 (ACSMS-SCR-028)'
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -12963,7 +13194,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面が表示された状態であること
+            <t xml:space="preserve">PDFファイルがダウンロードされること
 </t>
           </r>
           <r>
@@ -12980,15 +13211,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・「/login」へ遷移すること（クエリに `redirect` が付与されること）</t>
+            <t xml:space="preserve">・t_file_download に1件登録されること（download_type=3、file_name にPDFファイル名、record_count に対象件数、target_month に適用日の年月）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・t_log に監査ログが1件記録されること（log_type=1、operation=`EXPORT_PDF`、result_status=1、target_table=`t_file_download`）</t>
           </r>
         </is>
       </c>
@@ -13000,7 +13231,7 @@
       <c r="AD51" s="11" t="n"/>
       <c r="AE51" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF51" s="11" t="n"/>
@@ -13042,20 +13273,20 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="160" customHeight="1">
+    <row r="52" ht="256" customHeight="1">
       <c r="A52" s="44" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B52" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-036</t>
+          <t>ACSMS-TC-028-032</t>
         </is>
       </c>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="46" t="inlineStr">
         <is>
-          <t>バリデーションエラー応答形状（VALIDATION_ERROR）</t>
+          <t>トランザクション ロールバック</t>
         </is>
       </c>
       <c r="F52" s="10" t="n"/>
@@ -13064,7 +13295,8 @@
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・ダウンロード履歴登録時にDBエラーを発生させる準備ができている</t>
         </is>
       </c>
       <c r="K52" s="10" t="n"/>
@@ -13089,7 +13321,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsのNetworkタブでPOST「/api/v1/report/zougen-hanbaiten/export」に tekiyo_date を欠落させたリクエストボディを送信</t>
+            <t xml:space="preserve">「電子帳票作成」を実行する（DB登録の途中でエラーを注入する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DBで t_file_download・t_log の状態を確認</t>
           </r>
         </is>
       </c>
@@ -13115,15 +13364,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・レスポンスに `errors` 配列が含まれ、各要素が `{ field, message }` の形状であること</t>
+            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・t_file_download・t_log（log_type=1）のいずれも登録されないこと（ロールバックされること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・t_log にエラーログが1件記録されること（log_type=3、result_status=2）</t>
           </r>
         </is>
       </c>
@@ -13177,20 +13443,20 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="176" customHeight="1">
+    <row r="53" ht="224" customHeight="1">
       <c r="A53" s="44" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-037</t>
+          <t>ACSMS-TC-028-033</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
+          <t>対象0件（電子帳票作成）</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -13199,7 +13465,8 @@
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・指定した条件に対象データが存在しない</t>
         </is>
       </c>
       <c r="K53" s="10" t="n"/>
@@ -13224,7 +13491,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューまたは電子帳票作成相当のリクエストを上限回数まで連続送信する
+            <t xml:space="preserve">対象が存在しない適用日・条件で「電子帳票作成」を実行する
 </t>
           </r>
           <r>
@@ -13241,7 +13508,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>上限を超えて追加のリクエストを送信する</t>
+            <t>DBで t_file_download の登録件数を確認する</t>
           </r>
         </is>
       </c>
@@ -13267,7 +13534,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">上限回数までのリクエストが正常に処理されること
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`application/json` の `{ data: { reports: [] } }`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PDFファイルがダウンロードされないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-028-002）
 </t>
           </r>
           <r>
@@ -13284,7 +13567,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
+            <t>t_file_download にレコードが登録されないこと</t>
           </r>
         </is>
       </c>
@@ -13330,7 +13613,12 @@
       <c r="BH53" s="45" t="inlineStr"/>
       <c r="BI53" s="10" t="n"/>
       <c r="BJ53" s="11" t="n"/>
-      <c r="BK53" s="46" t="inlineStr"/>
+      <c r="BK53" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL53" s="10" t="n"/>
       <c r="BM53" s="10" t="n"/>
       <c r="BN53" s="10" t="n"/>
@@ -13338,135 +13626,74 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="192" customHeight="1">
-      <c r="A54" s="44" t="n">
-        <v>38</v>
-      </c>
-      <c r="B54" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-028-038</t>
-        </is>
-      </c>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ5: 共通エラーハンドリング（Common Error Handling）</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="46" t="inlineStr">
-        <is>
-          <t>システムエラー（INTERNAL_SERVER_ERROR）</t>
-        </is>
-      </c>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
       <c r="H54" s="10" t="n"/>
-      <c r="I54" s="11" t="n"/>
-      <c r="J54" s="46" t="inlineStr">
-        <is>
-          <t>・CHUOKAI でログイン済み
-・サーバー側で例外を発生させる準備ができている</t>
-        </is>
-      </c>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
       <c r="K54" s="10" t="n"/>
       <c r="L54" s="10" t="n"/>
       <c r="M54" s="10" t="n"/>
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="n"/>
-      <c r="P54" s="11" t="n"/>
-      <c r="Q54" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>サーバー側でDB接続エラー等を発生させた状態で「レポートプレビュー」を実行する</t>
-          </r>
-        </is>
-      </c>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
       <c r="R54" s="10" t="n"/>
       <c r="S54" s="10" t="n"/>
       <c r="T54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
-      <c r="W54" s="11" t="n"/>
-      <c r="X54" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メッセージ「システムエラーが発生しました。しばらくしてから再度お試しください。」が表示されること（ACSMS-MSG-028-003）</t>
-          </r>
-        </is>
-      </c>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
       <c r="Y54" s="10" t="n"/>
       <c r="Z54" s="10" t="n"/>
       <c r="AA54" s="10" t="n"/>
       <c r="AB54" s="10" t="n"/>
       <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="11" t="n"/>
-      <c r="AE54" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF54" s="11" t="n"/>
-      <c r="AG54" s="45" t="inlineStr"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
       <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="11" t="n"/>
-      <c r="AJ54" s="45" t="inlineStr"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="10" t="n"/>
-      <c r="AL54" s="11" t="n"/>
-      <c r="AM54" s="45" t="inlineStr"/>
+      <c r="AL54" s="10" t="n"/>
+      <c r="AM54" s="10" t="n"/>
       <c r="AN54" s="10" t="n"/>
-      <c r="AO54" s="11" t="n"/>
-      <c r="AP54" s="45" t="inlineStr"/>
+      <c r="AO54" s="10" t="n"/>
+      <c r="AP54" s="10" t="n"/>
       <c r="AQ54" s="10" t="n"/>
-      <c r="AR54" s="11" t="n"/>
-      <c r="AS54" s="45" t="inlineStr"/>
+      <c r="AR54" s="10" t="n"/>
+      <c r="AS54" s="10" t="n"/>
       <c r="AT54" s="10" t="n"/>
-      <c r="AU54" s="11" t="n"/>
-      <c r="AV54" s="45" t="inlineStr"/>
+      <c r="AU54" s="10" t="n"/>
+      <c r="AV54" s="10" t="n"/>
       <c r="AW54" s="10" t="n"/>
-      <c r="AX54" s="11" t="n"/>
-      <c r="AY54" s="45" t="inlineStr"/>
+      <c r="AX54" s="10" t="n"/>
+      <c r="AY54" s="10" t="n"/>
       <c r="AZ54" s="10" t="n"/>
-      <c r="BA54" s="11" t="n"/>
-      <c r="BB54" s="45" t="inlineStr"/>
+      <c r="BA54" s="10" t="n"/>
+      <c r="BB54" s="10" t="n"/>
       <c r="BC54" s="10" t="n"/>
-      <c r="BD54" s="11" t="n"/>
-      <c r="BE54" s="45" t="inlineStr"/>
+      <c r="BD54" s="10" t="n"/>
+      <c r="BE54" s="10" t="n"/>
       <c r="BF54" s="10" t="n"/>
-      <c r="BG54" s="11" t="n"/>
-      <c r="BH54" s="45" t="inlineStr"/>
+      <c r="BG54" s="10" t="n"/>
+      <c r="BH54" s="10" t="n"/>
       <c r="BI54" s="10" t="n"/>
-      <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BJ54" s="10" t="n"/>
+      <c r="BK54" s="10" t="n"/>
       <c r="BL54" s="10" t="n"/>
       <c r="BM54" s="10" t="n"/>
       <c r="BN54" s="10" t="n"/>
@@ -13474,20 +13701,20 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="128" customHeight="1">
+    <row r="55" ht="112" customHeight="1">
       <c r="A55" s="44" t="n">
         <v>39</v>
       </c>
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-039</t>
+          <t>ACSMS-TC-028-034</t>
         </is>
       </c>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="46" t="inlineStr">
         <is>
-          <t>ネットワーク切断</t>
+          <t>不正リクエストパラメータ（BAD_REQUEST）</t>
         </is>
       </c>
       <c r="F55" s="10" t="n"/>
@@ -13521,24 +13748,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevToolsのNetworkタブで「Offline」を選択し、ネットワークを切断する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>「レポートプレビュー」ボタンをクリックする</t>
+            <t>DevToolsのNetworkタブでGET「/api/v1/report/zougen-hanbaiten/preview?tekiyo_date=2026-05-01&amp;hanbaiten_id=abc」（数値項目に文字列）を送信</t>
           </r>
         </is>
       </c>
@@ -13564,32 +13774,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ネットワークが切断されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・ネットワークエラーのトーストが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・異常終了しないこと</t>
+            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。` または `error_code: VALIDATION_ERROR`）</t>
           </r>
         </is>
       </c>
@@ -13643,20 +13828,20 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="192" customHeight="1">
+    <row r="56" ht="208" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>40</v>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-028-040</t>
+          <t>ACSMS-TC-028-035</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="46" t="inlineStr">
         <is>
-          <t>SQLインジェクション入力の安全性</t>
+          <t>セッション切れ（UNAUTHORIZED）</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -13665,7 +13850,8 @@
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・管理ツールでセッションを強制失効させる準備ができている</t>
         </is>
       </c>
       <c r="K56" s="10" t="n"/>
@@ -13690,7 +13876,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevToolsのNetworkタブでGET「/api/v1/report/zougen-hanbaiten/preview」の tekiyo_date に `2026-05-01'; DROP TABLE t_dokusya_rireki; --` を指定して送信する
+            <t xml:space="preserve">増減連絡票（販売店）出力画面を開いた状態でセッションを強制失効させる
 </t>
           </r>
           <r>
@@ -13707,7 +13893,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DBで t_dokusya_rireki テーブルが存在することを確認する</t>
+            <t>「レポートプレビュー」ボタンをクリックする</t>
           </r>
         </is>
       </c>
@@ -13733,15 +13919,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・入力値がパラメータ化クエリにより literal として扱われ、SQLとして実行されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR` または `BAD_REQUEST`）
+            <t xml:space="preserve">画面が表示された状態であること
 </t>
           </r>
           <r>
@@ -13758,7 +13936,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>t_dokusya_rireki テーブルが削除されず存在すること</t>
+            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「/login」へ遷移すること（クエリに `redirect` が付与されること）</t>
           </r>
         </is>
       </c>
@@ -13812,33 +13998,1449 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
+    <row r="57" ht="160" customHeight="1">
+      <c r="A57" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-036</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>バリデーションエラー応答形状（VALIDATION_ERROR）</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevToolsのNetworkタブでPOST「/api/v1/report/zougen-hanbaiten/export」に tekiyo_date を欠落させたリクエストボディを送信</t>
+          </r>
+        </is>
+      </c>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・レスポンスに `errors` 配列が含まれ、各要素が `{ field, message }` の形状であること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF57" s="11" t="n"/>
+      <c r="AG57" s="45" t="inlineStr"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="11" t="n"/>
+      <c r="AJ57" s="45" t="inlineStr"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="11" t="n"/>
+      <c r="AM57" s="45" t="inlineStr"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="11" t="n"/>
+      <c r="AP57" s="45" t="inlineStr"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="11" t="n"/>
+      <c r="AS57" s="45" t="inlineStr"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="11" t="n"/>
+      <c r="AV57" s="45" t="inlineStr"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="11" t="n"/>
+      <c r="AY57" s="45" t="inlineStr"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="11" t="n"/>
+      <c r="BB57" s="45" t="inlineStr"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="11" t="n"/>
+      <c r="BE57" s="45" t="inlineStr"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="11" t="n"/>
+      <c r="BH57" s="45" t="inlineStr"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="11" t="n"/>
+      <c r="BK57" s="46" t="inlineStr"/>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="176" customHeight="1">
+      <c r="A58" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-037</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビューまたは電子帳票作成相当のリクエストを上限回数まで連続送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>上限を超えて追加のリクエストを送信する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">上限回数までのリクエストが正常に処理されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="11" t="n"/>
+      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="11" t="n"/>
+      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="11" t="n"/>
+      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="11" t="n"/>
+      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="11" t="n"/>
+      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="11" t="n"/>
+      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="11" t="n"/>
+      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="11" t="n"/>
+      <c r="BK58" s="46" t="inlineStr"/>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="192" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-038</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>システムエラー（INTERNAL_SERVER_ERROR）</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・サーバー側で例外を発生させる準備ができている</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>サーバー側でDB接続エラー等を発生させた状態で「レポートプレビュー」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メッセージ「システムエラーが発生しました。しばらくしてから再度お試しください。」が表示されること（ACSMS-MSG-028-003）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr"/>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="128" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-039</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>ネットワーク切断</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevToolsのNetworkタブで「Offline」を選択し、ネットワークを切断する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「レポートプレビュー」ボタンをクリックする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ネットワークが切断されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ネットワークエラーのトーストが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・異常終了しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="192" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-040</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>SQLインジェクション入力の安全性</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevToolsのNetworkタブでGET「/api/v1/report/zougen-hanbaiten/preview」の tekiyo_date に `2026-05-01'; DROP TABLE t_dokusya_rireki; --` を指定して送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DBで t_dokusya_rireki テーブルが存在することを確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・入力値がパラメータ化クエリにより literal として扱われ、SQLとして実行されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR` または `BAD_REQUEST`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>t_dokusya_rireki テーブルが削除されず存在すること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: 集計対象・販売店候補（Scope / Hanbaiten Options）</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="10" t="n"/>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="10" t="n"/>
+      <c r="AF62" s="10" t="n"/>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="10" t="n"/>
+      <c r="AM62" s="10" t="n"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="10" t="n"/>
+      <c r="AP62" s="10" t="n"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="10" t="n"/>
+      <c r="AS62" s="10" t="n"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="10" t="n"/>
+      <c r="AV62" s="10" t="n"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="10" t="n"/>
+      <c r="AY62" s="10" t="n"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="10" t="n"/>
+      <c r="BB62" s="10" t="n"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="10" t="n"/>
+      <c r="BE62" s="10" t="n"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="10" t="n"/>
+      <c r="BH62" s="10" t="n"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="10" t="n"/>
+      <c r="BK62" s="10" t="n"/>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="450" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-048</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>集計対象を紙版のみに限定（#56408）</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`report.export_zougen_hanbaiten` 権限あり）
+・適用日を 2026/09/01 とし、同日に増減報告対象（`zougen_hokoku_flg = true`）の履歴を持つ購読者を以下のとおり用意すること（いずれも実在の販売店 A 配下）
+・(a) 紙版（dokusya_shubetsu=1）で 1 → 3 部の増部 1件
+・(b) 併読（3）で部数変更 1件
+・(c) 電子版（2）・承認済（denshi_shonin_status=1）1件
+・(d) 電子版（2）・未承認 1件</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">適用日 2026/09/01 でプレビューを表示し、対象となる購読者を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">PDF を出力し、販売店 A の増部数・減部数を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(b) 併読の購読者が出力に含まれるか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(c) 電子版・承認済の購読者が出力に含まれるか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(a) のみを残し他を削除した状態で出力し、件数が一致することを確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**(a) 紙版 1件のみ**が対象となること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店 A の増部数が (a) の増分（+2部）のみで構成されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**含まれないこと**。併読には「配達部数の増減を販売店へ伝える」という本帳票の目的に対応する変動が無いため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**含まれないこと**。従来は「電子版は承認済のみ集計」という条件だったが、紙版限定に包含されるため廃止した（顧客要件2026-08 / #56408）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力内容が変わらないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・本帳票は販売店へ配達部数の増減を伝えるもので、電子版・併読には配達という概念が無い（電子版単独はダミー販売店に紐づく）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・SCR-029 増減通知（日本農業新聞）も同じく紙版限定だが、条件は各画面が個別に持つ（共通化していないため、片方だけ変更されると乖離する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・購読者名簿（SCR-026）は帳票種別ごとに対象が異なる（管理支店別は併読・電子版も対象）。本画面の条件をそのまま流用しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr"/>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="450" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-049</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>販売店候補から電子版ダミー販売店を除外（#56597）</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`report.export_zougen_hanbaiten` 権限あり）
+・自JAに電子版ダミー販売店（`hanbaiten_code = 9999999999`）が存在し、電子版購読者が紐づいていること
+・実在の販売店が 2 件以上存在すること
+・廃店フラグ（`haiten_flg = true`）の販売店も 1 件用意すること</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力条件の「販売店」プルダウンを開き、候補を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`GET /api/v1/hanbaiten/dropdown` のリクエストパラメータを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">廃店の販売店が候補に出るか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevTools からダミー販売店の `hanbaiten_id` を直接指定して出力APIを呼び出す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">実在かつ廃店でない販売店のみが候補に表示され、**ダミー販売店（9999999999）が候補に出ないこと**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dummy=exclude` が指定されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">廃店の販売店も候補に出ないこと（集計SQL側でも `h.haiten_flg = false` で除外している）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">0 件となること。本帳票の集計対象は紙版のみで、ダミーに紐づくのは電子版読者のみのため、選べたとしても必ず0件になる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版ダミー販売店は「電子版読者を紐づける受け皿」であり実在の販売店ではない（`t_dokusya.hanbaiten_id` が NOT NULL のために用意している）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・同じ除外は購読者名簿（SCR-026）の販売店別にも適用される（ACSMS-TC-026-044 参照）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="751">
+  <mergeCells count="871">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AP50:AR50"/>
-    <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="E52:I52"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AV57:AX57"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
+    <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
@@ -13855,10 +15457,12 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
+    <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
@@ -13880,28 +15484,40 @@
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="AY57:BA57"/>
+    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -13923,7 +15539,6 @@
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="AM50:AO50"/>
-    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
     <mergeCell ref="AP16:AR16"/>
     <mergeCell ref="BH24:BJ24"/>
@@ -13955,8 +15570,8 @@
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
-    <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -13965,19 +15580,27 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E49:I49"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="BH45:BJ45"/>
@@ -14000,6 +15623,8 @@
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14007,9 +15632,11 @@
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="J23:P23"/>
+    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
+    <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -14027,6 +15654,7 @@
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="AS35:AU35"/>
+    <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
@@ -14036,17 +15664,21 @@
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
+    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14057,11 +15689,14 @@
     <mergeCell ref="AC6:AE6"/>
     <mergeCell ref="AG39:AI39"/>
     <mergeCell ref="BB17:BD17"/>
+    <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
@@ -14069,12 +15704,15 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="AS54:AU54"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="AS41:AU41"/>
+    <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="AV55:AX55"/>
@@ -14087,18 +15725,21 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
@@ -14107,8 +15748,11 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AV45:AX45"/>
@@ -14128,32 +15772,46 @@
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
+    <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
+    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
+    <mergeCell ref="A54:BQ54"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
+    <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14173,8 +15831,10 @@
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="Q49:W49"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
@@ -14187,9 +15847,12 @@
     <mergeCell ref="BH17:BJ17"/>
     <mergeCell ref="E48:I48"/>
     <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
+    <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="BH19:BJ19"/>
     <mergeCell ref="BB22:BD22"/>
@@ -14198,11 +15861,10 @@
     <mergeCell ref="BK30:BQ30"/>
     <mergeCell ref="BK36:BQ36"/>
     <mergeCell ref="AS47:AU47"/>
-    <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
-    <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -14210,22 +15872,34 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AS58:AU58"/>
+    <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
+    <mergeCell ref="BE49:BG49"/>
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14236,7 +15910,9 @@
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
+    <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
@@ -14257,7 +15933,6 @@
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
-    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
@@ -14282,6 +15957,7 @@
     <mergeCell ref="AS25:AU25"/>
     <mergeCell ref="BB42:BD42"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
@@ -14300,20 +15976,26 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
+    <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
@@ -14321,10 +16003,12 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
@@ -14333,6 +16017,7 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14348,27 +16033,34 @@
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
     <mergeCell ref="E27:I27"/>
+    <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
-    <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="A62:BQ62"/>
     <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
+    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14376,12 +16068,14 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
-    <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
@@ -14406,7 +16100,7 @@
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="J27:P27"/>
@@ -14418,6 +16112,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -14428,7 +16123,6 @@
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="AV38:AX38"/>
-    <mergeCell ref="A49:BQ49"/>
     <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
@@ -14440,9 +16134,12 @@
     <mergeCell ref="X31:AD31"/>
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="BB25:BD25"/>
+    <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
+    <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
@@ -14456,27 +16153,31 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E54:I54"/>
+    <mergeCell ref="X49:AD49"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="AE27:AF27"/>
-    <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -14489,27 +16190,32 @@
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
-    <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ37:AL37"/>
+    <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="AY20:BA20"/>
     <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
+    <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
-    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="B50:D50"/>
+    <mergeCell ref="AP57:AR57"/>
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
@@ -14518,23 +16224,27 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
     <mergeCell ref="X55:AD55"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
-    <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
+    <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
@@ -14542,8 +16252,10 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -14565,15 +16277,17 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE48 AE50:AE56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE53 AE55:AE61 AE63:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG48 AG50:AG56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG53 AG55:AG61 AG63:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV48 AV50:AV56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV53 AV55:AV61 AV63:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1415,26 +1415,84 @@
       <c r="AG3" s="10" t="n"/>
       <c r="AH3" s="11" t="n"/>
     </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>顧客報告 #57976 の不具合修正に伴い TC-028-026 を書き換え：廃店(haiten_flg=true)を宛先とする報告のみを抑止し、営業中の転出元側の減部報告は行単位で消えないことを確認する内容に変更（API設計書 v1.4）。TC-028-049 の廃店に関する補足説明も実装（グルーピング処理での抑止）に合わせて修正。</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12302,7 +12360,7 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="64" customHeight="1">
+    <row r="46" ht="192" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>31</v>
       </c>
@@ -12315,7 +12373,7 @@
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>廃店の除外</t>
+          <t>廃店を宛先とする報告の抑止（転出元は営業中のまま計上・#57976）</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -12325,7 +12383,8 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・廃店（haiten_flg=true）に紐づく履歴が存在する</t>
+・購読者が営業中の販売店A（haiten_flg=false）から廃店B（haiten_flg=true）へ
+販売店変更された履歴（同一適用日・zougen_hokoku_flg=true）が存在する</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -12376,7 +12435,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>廃店（haiten_flg=true）に紐づくレコードが抽出されないこと</t>
+            <t xml:space="preserve">販売店A（営業中・転出元）の帳票に、該当購読者の減部（`genbu`。`{変更前部数} → 0`）が
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">計上されること——廃店への転出であっても行自体は除外されず、旧店側の報告は消えない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店B（廃店・転入先）を宛先とする報告は生成されないこと（`reports` に
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>販売店Bのグループが含まれない）</t>
           </r>
         </is>
       </c>
@@ -15305,7 +15388,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">廃店の販売店も候補に出ないこと（集計SQL側でも `h.haiten_flg = false` で除外している）
+            <t xml:space="preserve">廃店の販売店も候補に出ないこと（`/hanbaiten/dropdown` 側の絞り込み。集計SQL側は
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">行単位では除外せず、報告の宛先となる店舗が廃店の場合にのみ抑止する — #57976・
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-TC-028-026 参照）
 </t>
           </r>
           <r>

--- a/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1467,16 +1467,81 @@
       <c r="AG4" s="10" t="n"/>
       <c r="AH4" s="11" t="n"/>
     </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="18" t="inlineStr"/>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>顧客要件2026-08：TC-028-050を新規追加。統廃合販売店読者移行画面（旧: 購読者販売店一括置換画面・SCR-015）経由の変更（`hanbaiten_tohaigo_flg=true`）が本帳票の集計対象から除外され、購読者情報登録画面（SCR-011）経由の変更（false）は引き続き対象となることを確認する（API設計書 v1.7）。</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="10" t="n"/>
+      <c r="AB5" s="11" t="n"/>
+      <c r="AC5" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="10" t="n"/>
+      <c r="AH5" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
     <mergeCell ref="O3:V3"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="AC5:AH5"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="W3:AB3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="AC4:AH4"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="B4:E4"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="B3:E3"/>
@@ -1491,6 +1556,7 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
+    <mergeCell ref="W5:AB5"/>
     <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
   </mergeCells>
@@ -6355,7 +6421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ64"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15492,12 +15558,7 @@
       <c r="BH64" s="45" t="inlineStr"/>
       <c r="BI64" s="10" t="n"/>
       <c r="BJ64" s="11" t="n"/>
-      <c r="BK64" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK64" s="46" t="inlineStr"/>
       <c r="BL64" s="10" t="n"/>
       <c r="BM64" s="10" t="n"/>
       <c r="BN64" s="10" t="n"/>
@@ -15505,8 +15566,202 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
+    <row r="65" ht="368" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-050</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>販売店統廃合フラグ（hanbaiten_tohaigo_flg）=trueの履歴を集計対象から除外（顧客要件2026-08）</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`report.export_zougen_hanbaiten` 権限あり）
+・適用日を 2026/09/01 とし、同日に増減報告対象（`zougen_hokoku_flg = true`・紙版）の履歴を持つ購読者を以下のとおり用意すること（いずれも実在の販売店 A 配下）
+・(a) 統廃合販売店読者移行画面（旧: 購読者販売店一括置換画面・SCR-015）から販売店を置換した購読者 1件（`hanbaiten_tohaigo_flg = true`）
+・(b) 購読者情報登録画面（SCR-011）で販売店を変更した購読者 1件（`hanbaiten_tohaigo_flg = false`）</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">適用日 2026/09/01 でプレビューを表示する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>PDF を出力し、販売店 A の増減部数の内訳を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**(b) のみ**が対象となること。(a)（統廃合販売店読者移行画面経由）は集計対象から除外される
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店 A の増減部数が (b) の変動のみで構成されていること。(a) による部数変動は含まれない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・本フラグは統廃合販売店読者移行画面から書き込まれた変更（合併・閉店による読者の付け替え）を、実際の増減として販売店へ通知しないための除外条件
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・SCR-029 増減通知（日本農業新聞）は本フラグの影響を受けず、(a)(b) とも全件反映される（仕様変更なし）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="871">
+  <mergeCells count="888">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -15537,6 +15792,7 @@
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -15597,6 +15853,7 @@
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
@@ -15702,6 +15959,7 @@
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -15752,6 +16010,7 @@
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
@@ -15765,6 +16024,7 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
@@ -15778,6 +16038,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -15814,6 +16075,7 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
@@ -15847,6 +16109,7 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
@@ -15964,6 +16227,7 @@
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -16006,6 +16270,7 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
@@ -16074,6 +16339,7 @@
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AV64:AX64"/>
@@ -16160,6 +16426,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -16201,6 +16468,7 @@
     <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
@@ -16256,6 +16524,7 @@
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E61:I61"/>
@@ -16270,6 +16539,7 @@
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
@@ -16297,6 +16567,7 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
@@ -16351,6 +16622,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -16380,13 +16652,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE53 AE55:AE61 AE63:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE53 AE55:AE61 AE63:AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG53 AG55:AG61 AG63:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG53 AG55:AG61 AG63:AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV53 AV55:AV61 AV63:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV53 AV55:AV61 AV63:AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
